--- a/migracion/archivo.xlsx
+++ b/migracion/archivo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jhon de quesada\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jhon de quesada\Documents\proyectos\vidaysalud\admin-dashboard-responsive-8dd\public\migracion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28C5451-BB6A-44C2-B31A-9E10FF15A926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57BFEE0-C652-4ACF-87A7-B8590D549EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -377,7 +377,8 @@
     <col min="10" max="12" width="11.42578125" customWidth="1"/>
     <col min="13" max="13" width="11.85546875" customWidth="1"/>
     <col min="14" max="14" width="21" customWidth="1"/>
-    <col min="15" max="26" width="11.42578125" customWidth="1"/>
+    <col min="15" max="15" width="23" customWidth="1"/>
+    <col min="16" max="26" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
@@ -1425,7 +1426,12 @@
     <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O715" xr:uid="{F700D3D4-FF4D-4BFC-97B9-276200BA2EC4}">
+      <formula1>"HEMODINAMIA,MARCAPASO"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>